--- a/data/Linkedin Summarize.xlsx
+++ b/data/Linkedin Summarize.xlsx
@@ -3,9 +3,10 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="customer_info" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="post_details" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="weekly_summary" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="cutomer_info" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="phantom_result" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="post_details" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="weekly_summary" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -13,125 +14,349 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="98">
+  <si>
+    <t>profileUrl</t>
+  </si>
   <si>
     <t>customer_name</t>
   </si>
   <si>
+    <t>postUrl</t>
+  </si>
+  <si>
+    <t>linkedin_profile_url</t>
+  </si>
+  <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>ABC Information Solutions</t>
+  </si>
+  <si>
+    <t>timestamp</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/abc-information-solutions/</t>
+  </si>
+  <si>
+    <t>imgUrl</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>postContent</t>
+  </si>
+  <si>
     <t>week_start</t>
   </si>
   <si>
+    <t>likeCount</t>
+  </si>
+  <si>
     <t>week_end</t>
   </si>
   <si>
+    <t>commentCount</t>
+  </si>
+  <si>
+    <t>content_summary</t>
+  </si>
+  <si>
+    <t>repostCount</t>
+  </si>
+  <si>
+    <t>postDate</t>
+  </si>
+  <si>
+    <t>processing_status</t>
+  </si>
+  <si>
+    <t>action</t>
+  </si>
+  <si>
+    <t>processing_error</t>
+  </si>
+  <si>
+    <t>authorUrl</t>
+  </si>
+  <si>
+    <t>processed_at</t>
+  </si>
+  <si>
+    <t>viewCount</t>
+  </si>
+  <si>
+    <t>postTimestamp</t>
+  </si>
+  <si>
+    <t>videoUrl</t>
+  </si>
+  <si>
+    <t>sharedPostUrl</t>
+  </si>
+  <si>
+    <t>sharedJobUrl</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Invalid input</t>
+  </si>
+  <si>
+    <t>2026-09-20T14:08:21.371Z</t>
+  </si>
+  <si>
+    <t>Airtasker</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/airtasker/posts/?feedView=all</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/feed/update/urn:li:activity:7500039335921188864</t>
+  </si>
+  <si>
+    <t>2026-09-20T14:08:35.690Z</t>
+  </si>
+  <si>
+    <t>https://media.licdn.com/dms/image/v2/D5622AQHAvBL96Aas1Q/feedshare-shrink_800/B56aBV.CAdJkAc-/0/1788148720417?e=1791417600&amp;v=beta&amp;t=Ce20FtfF6ky0UPRtObLlrBmsjfN5uvHTGQrppK3zFUM</t>
+  </si>
+  <si>
+    <t>AVANTCHA Tea</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/avantcha/</t>
+  </si>
+  <si>
+    <t>Image</t>
+  </si>
+  <si>
     <t>post_count</t>
   </si>
   <si>
     <t>weekly_synthesis</t>
   </si>
   <si>
-    <t>processed_at</t>
-  </si>
-  <si>
-    <t>processing_status</t>
-  </si>
-  <si>
-    <t>content_summary</t>
-  </si>
-  <si>
-    <t>processing_error</t>
-  </si>
-  <si>
-    <t>linkedin_profile_url</t>
-  </si>
-  <si>
-    <t>ABC Information Solutions</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/company/abc-information-solutions/</t>
-  </si>
-  <si>
-    <t>Airtasker</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/company/airtasker/posts/?feedView=all</t>
-  </si>
-  <si>
-    <t>AVANTCHA Tea</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/company/avantcha/</t>
+    <t>At ABCis, we do our best work when we channel a clear focus and fresh energy into our core purpose. We're anchoring FY27 with the mantra : Be Curious &amp; Find Your Inner Poet.
+We believe our standard for excellence happens at the perfect intersection of structure and artistry.
+On one side, it’s about celebrating the hard, foundational work - ensuring our operations are rock-solid, friction-free, and completely dependable. On the other hand, it’s about empowering our team to look beyond the routine, stay genuinely curious, and approach daily challenges with creative perspective.
+Here’s to pushing forward together with strong foundations, bold ideas, and shared growth!
+#BeCurious #FindingOurInnerPoet #abcis</t>
   </si>
   <si>
     <t>Bed Space Design</t>
   </si>
   <si>
+    <t>2w</t>
+  </si>
+  <si>
+    <t>Post</t>
+  </si>
+  <si>
     <t>https://www.linkedin.com/company/bed-space-design/</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/company/abc-information-solutions</t>
+  </si>
+  <si>
+    <t>2026-08-31T03:58:41.676Z</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/feed/update/urn:li:activity:7494543887252746242</t>
+  </si>
+  <si>
     <t>Biarri</t>
   </si>
   <si>
     <t>https://www.linkedin.com/company/biarri/</t>
   </si>
   <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>Hiring: Business Analyst (FMCG Focus) 🚀
+Our sister company within the Vela Software / Centaurus group is looking for a Business Analyst to join the team and play a critical role in bridging the gap between operations, system capabilities, and strategy.
+If you have a knack for untangling operational workflows and driving system efficiencies in the FMCG space, this role is built for you.
+Key Focus Areas
+- Systems Expertise: Heavy focus on Back Office and Head Office systems (ERP, supply chain, inventory, trade promotion, or master data management).
+- Process Optimization: Mapping as-is processes and designing to-be solutions to streamline FMCG operations.
+- Requirements Gathering: Translating complex business needs into clear, actionable functional specifications for technical teams.
+- Stakeholder Management: Partnering with cross-functional leaders across business units to drive system adoption and efficiency.
+What We’re Looking For:
+- Proven experience as a Business Analyst, ideally within the FMCG or CPG sector.
+- Strong background working directly with Head Office and Back Office software environments.
+- Sharp analytical skills, a practical problem-solving mindset, and top-tier communication skills.
+Why Centaurus / Vela Software?
+You get the agility and ownership of a focused business unit, backed by the stability, resources, and global network of Constellation Software / Vela.
+Know someone who would be a great fit? Tag them below or send a direct message to learn more!
+#Hiring #BusinessAnalyst #FMCG #JobOpportunity #VelaSoftware #Centaurus #TechJobs #SupplyChain</t>
+  </si>
+  <si>
+    <t>1mo</t>
+  </si>
+  <si>
+    <t>2026-08-16T00:01:44.613Z</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/feed/update/urn:li:activity:7488055050276130816</t>
+  </si>
+  <si>
     <t>Biarri Networks</t>
   </si>
   <si>
+    <t>2026-09-20T14:08:35.691Z</t>
+  </si>
+  <si>
     <t>https://www.linkedin.com/company/biarrinetworks/</t>
   </si>
   <si>
+    <t>https://media.licdn.com/dms/image/v2/D5622AQGmkzQD3fGZiw/feedshare-shrink_800/B56Z.rqY5lIcAk-/0/1785291444081?e=1791417600&amp;v=beta&amp;t=OcOe8c6T3NywI1zt8jxW7buNLTn5WrQvVsQ8rUV6lRk</t>
+  </si>
+  <si>
     <t>Books + Records</t>
   </si>
   <si>
     <t>https://www.linkedin.com/company/booksandrecords/</t>
   </si>
   <si>
-    <t>post_url</t>
-  </si>
-  <si>
-    <t>post_date</t>
-  </si>
-  <si>
-    <t>post_content</t>
-  </si>
-  <si>
-    <t>post_type</t>
-  </si>
-  <si>
-    <t>like_count</t>
-  </si>
-  <si>
-    <t>comment_count</t>
-  </si>
-  <si>
-    <t>repost_count</t>
-  </si>
-  <si>
-    <t>view_count</t>
-  </si>
-  <si>
-    <t>img_url</t>
-  </si>
-  <si>
-    <t>video_url</t>
+    <t>A new chapter for ABCis: we've been acquired by Vela APX, part of Vela Software Group within Constellation Software Inc.
+Joining Vela APX's global network of vertical market software businesses is a huge milestone for us. Constellation is known for buying great software businesses and backing them for the long term — which means this partnership gives us the runway to accelerate our growth and bring even more value to the 1,000+ independent retail businesses we proudly serve across Australia.
+As we look ahead, we want to take a moment to celebrate Michael Beer, who has led ABCis for the past 10 years. Under his leadership, ABCis grew into a trusted technology and data partner across the grocery, fuel, pharmacy, and hospitality industries. Thank you, Michael, for your vision, dedication, and the lasting impact you've had on our team and community.
+We're equally excited to announce that Sam Davies is stepping up as our new General Manager. Having been an integral part of ABCis for 12 years, Sam brings deep domain expertise, strong relationships across the industry, and an unmatched understanding of our business — the right person to lead ABCis into this next era.
+Our backing is bigger than ever, but our mission hasn't changed: helping independent retailers thrive through smart technology and data services.
+A massive thank you to our team, clients, and partners who have made this journey so incredible. We're just getting started.</t>
+  </si>
+  <si>
+    <t>2026-07-29T02:17:25.321Z</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/feed/update/urn:li:activity:7462626448319750144</t>
+  </si>
+  <si>
+    <t>https://media.licdn.com/dms/image/v2/D5622AQHaQ7NmB2yLSw/feedshare-shrink_800/B56Z5CTNbmKwAc-/0/1779228792794?e=1791417600&amp;v=beta&amp;t=NvHOtgEJKnTW7ptWMESoc51B0gFOT0UcN37SxXzqtDk</t>
+  </si>
+  <si>
+    <t>Our team recently attended the Direct2Store Expo in Sydney!
+We loved sharing how we help independent retailers improve performance through smarter systems and data-driven insights. Great to see so many familiar faces and meet new ones!</t>
+  </si>
+  <si>
+    <t>4mo</t>
+  </si>
+  <si>
+    <t>2026-05-19T22:13:14.174Z</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/feed/update/urn:li:activity:7444866152943595520</t>
+  </si>
+  <si>
+    <t>https://media.licdn.com/dms/image/v2/D5622AQFxnxvmRNM9lw/feedshare-shrink_800/B56Z083ww3KkAc-/0/1774842744081?e=1791417600&amp;v=beta&amp;t=uesiXCDLCSWXXO--8gn4SVcFVCDFdHd3CImUePxIYCo</t>
+  </si>
+  <si>
+    <t>Happy Easter from our team to yours 🐣
+We will be taking a short break during Good Friday and Easter Monday (03/04, 06/04), we hope you have a wonderful long weekend with family and friends!</t>
+  </si>
+  <si>
+    <t>5mo</t>
+  </si>
+  <si>
+    <t>2026-03-31T22:00:09.786Z</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/feed/update/urn:li:activity:7435478680614686722</t>
+  </si>
+  <si>
+    <t>2026-09-20T14:08:35.692Z</t>
+  </si>
+  <si>
+    <t>https://media.licdn.com/dms/image/v2/D5622AQEmiChZxF4sBQ/feedshare-shrink_800/B56ZzAgddqKEAg-/0/1772756260977?e=1791417600&amp;v=beta&amp;t=lqRLBFsiMA1ogoS6mluxD6t9eMdTcseZ0ID_RxZe6h4</t>
+  </si>
+  <si>
+    <t>Congratulations to the team at IGA Inveresk on the opening of a brand-new store!
+We are thrilled to officially welcome this new location to the ABCis family. As a valued, long-term partner, it is a privilege to support their continued growth.
+We look forward to seeing the IGA Inveresk team thrive in their new store, welcome!
+#IGATasmania #RetailGrowth #IndependentRetail #ABCis</t>
+  </si>
+  <si>
+    <t>6mo</t>
+  </si>
+  <si>
+    <t>2026-03-06T00:17:41.972Z</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/feed/update/urn:li:activity:7427493258416742400</t>
+  </si>
+  <si>
+    <t>https://media.licdn.com/dms/image/v2/D5622AQEBpEsyCXnpQA/feedshare-shrink_800/B56ZxPBwnCIYAk-/0/1770852387519?e=1791417600&amp;v=beta&amp;t=s1fU5kc606DKDa1MGEcgcpf94ENVd6Mu7nJxy9jUPQM</t>
+  </si>
+  <si>
+    <t>We are excited to welcome Molly to the ABCis team as our new office manager!
+Molly joins us while currently pursuing her studies at the University of Sydney, but outside of work and study, Molly is an avid hiker and baker. 
+She looks forward to joining the ABCis team and supporting internal operations!</t>
+  </si>
+  <si>
+    <t>7mo</t>
+  </si>
+  <si>
+    <t>2026-02-11T23:26:28.958Z</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/feed/update/urn:li:activity:7399292070474993664</t>
+  </si>
+  <si>
+    <t>https://media.licdn.com/dms/image/v2/D5622AQHtSGuq075ubg/feedshare-shrink_800/B56ZqkcgiUKwAg-/0/1763695572073?e=1791417600&amp;v=beta&amp;t=oEkT_A84DyZ_vcW4kIhZiWmngB2yAhVTR17zLOiJ3-8</t>
+  </si>
+  <si>
+    <t>Happy Holidays from our team to yours! 
+We had an absolute blast at our Christmas party this year, letting loose at Zero Latency VR. Safe to say, our retail skills are way better than our VR gaming skills! 😂 
+A huge congratulations to our incredible click manager, Kara, for being crowned Employee of the Year! We're incredibly proud of our team and all we've accomplished together.</t>
+  </si>
+  <si>
+    <t>9mo</t>
+  </si>
+  <si>
+    <t>2025-11-26T03:45:01.800Z</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/feed/update/urn:li:activity:7397473836579012608</t>
+  </si>
+  <si>
+    <t>2026-09-20T14:08:35.693Z</t>
+  </si>
+  <si>
+    <t>https://media.licdn.com/dms/image/v2/D5622AQEh95nnuK6SFg/feedshare-shrink_800/B56ZqkbOJqI8Ag-/0/1763695199856?e=1791417600&amp;v=beta&amp;t=B0j_I0ia-_LZmt5gjUL4qaGPcr3E7E8jZ44u8gR0a3Q</t>
+  </si>
+  <si>
+    <t>Management Challenge: You know you need to change your internal processes, but how do you get from A to Z?
+The gap between realising your operations are inefficient and actually making them streamlined can feel massive. It requires expertise in standardisation, process re-engineering, and long-term vision.
+ABCis Consulting Services is your management guide. We leverage our unrivalled skill set, gained from over 100 years of retail experience, and working with over 1000s of retailers. 
+We don't just offer generic advice; we take the time to deeply understand your operations and make specific recommendations and guide you through the journey to operation efficiency.
+End the overwhelm and gain expert guidance. Get in touch for a chat, or check out our full product suite! ⚙️💡</t>
+  </si>
+  <si>
+    <t>2025-11-21T03:20:01.058Z</t>
+  </si>
+  <si>
+    <t>Export limit reached - Get more with our premium plans</t>
+  </si>
+  <si>
+    <t>Upgrade to export all your data with the link below:</t>
+  </si>
+  <si>
+    <t>https://phbuster.io/upgrade</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color theme="1"/>
-      <name val="Menlo"/>
     </font>
     <font>
       <color theme="1"/>
@@ -141,6 +366,16 @@
     <font>
       <u/>
       <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color theme="1"/>
+      <name val="Menlo"/>
     </font>
   </fonts>
   <fills count="2">
@@ -157,7 +392,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -168,6 +403,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -187,6 +425,10 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -400,67 +642,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>9</v>
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>11</v>
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
+      <c r="A3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>15</v>
+      <c r="A4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>17</v>
+      <c r="A5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>19</v>
+      <c r="A6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>21</v>
+      <c r="A7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>23</v>
+      <c r="A8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -484,67 +726,498 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="4" max="4" width="18.63"/>
+    <col customWidth="1" min="1" max="1" width="23.75"/>
+    <col customWidth="1" min="7" max="7" width="40.0"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="G1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="2" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="O1" s="2" t="s">
+      <c r="D3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>5</v>
+      <c r="B4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="1">
+        <v>29.0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H9" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="A3"/>
+    <hyperlink r:id="rId2" ref="B3"/>
+    <hyperlink r:id="rId3" ref="E3"/>
+    <hyperlink r:id="rId4" ref="M3"/>
+    <hyperlink r:id="rId5" ref="A4"/>
+    <hyperlink r:id="rId6" ref="B4"/>
+    <hyperlink r:id="rId7" ref="M4"/>
+    <hyperlink r:id="rId8" ref="A5"/>
+    <hyperlink r:id="rId9" ref="B5"/>
+    <hyperlink r:id="rId10" ref="E5"/>
+    <hyperlink r:id="rId11" ref="M5"/>
+    <hyperlink r:id="rId12" ref="A6"/>
+    <hyperlink r:id="rId13" ref="B6"/>
+    <hyperlink r:id="rId14" ref="E6"/>
+    <hyperlink r:id="rId15" ref="M6"/>
+    <hyperlink r:id="rId16" ref="A7"/>
+    <hyperlink r:id="rId17" ref="B7"/>
+    <hyperlink r:id="rId18" ref="E7"/>
+    <hyperlink r:id="rId19" ref="M7"/>
+    <hyperlink r:id="rId20" ref="A8"/>
+    <hyperlink r:id="rId21" ref="B8"/>
+    <hyperlink r:id="rId22" ref="E8"/>
+    <hyperlink r:id="rId23" ref="M8"/>
+    <hyperlink r:id="rId24" ref="A9"/>
+    <hyperlink r:id="rId25" ref="B9"/>
+    <hyperlink r:id="rId26" ref="E9"/>
+    <hyperlink r:id="rId27" ref="M9"/>
+    <hyperlink r:id="rId28" ref="A10"/>
+    <hyperlink r:id="rId29" ref="B10"/>
+    <hyperlink r:id="rId30" ref="E10"/>
+    <hyperlink r:id="rId31" ref="M10"/>
+    <hyperlink r:id="rId32" ref="A11"/>
+    <hyperlink r:id="rId33" ref="B11"/>
+    <hyperlink r:id="rId34" ref="E11"/>
+    <hyperlink r:id="rId35" ref="M11"/>
+    <hyperlink r:id="rId36" ref="A16"/>
+  </hyperlinks>
+  <drawing r:id="rId37"/>
 </worksheet>
 </file>
 
@@ -555,33 +1228,71 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
+    <col customWidth="1" min="4" max="4" width="18.63"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
     <col customWidth="1" min="7" max="7" width="14.0"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>8</v>
+      <c r="B1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
